--- a/data/nzd0403/nzd0403.xlsx
+++ b/data/nzd0403/nzd0403.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N271"/>
+  <dimension ref="A1:N272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13136,7 +13136,7 @@
         <v>340.12</v>
       </c>
       <c r="H271" t="n">
-        <v>337.66</v>
+        <v>350.06</v>
       </c>
       <c r="I271" t="n">
         <v>366.1</v>
@@ -13151,11 +13151,59 @@
         <v>373.63</v>
       </c>
       <c r="M271" t="n">
-        <v>307.43</v>
+        <v>332.73</v>
       </c>
       <c r="N271" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:46+00:00</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>301.09</v>
+      </c>
+      <c r="C272" t="n">
+        <v>304.62</v>
+      </c>
+      <c r="D272" t="n">
+        <v>322.19</v>
+      </c>
+      <c r="E272" t="n">
+        <v>326.88</v>
+      </c>
+      <c r="F272" t="n">
+        <v>345.92</v>
+      </c>
+      <c r="G272" t="n">
+        <v>363.94</v>
+      </c>
+      <c r="H272" t="n">
+        <v>390.67</v>
+      </c>
+      <c r="I272" t="n">
+        <v>386.35</v>
+      </c>
+      <c r="J272" t="n">
+        <v>367.72</v>
+      </c>
+      <c r="K272" t="n">
+        <v>382.43</v>
+      </c>
+      <c r="L272" t="n">
+        <v>390.7</v>
+      </c>
+      <c r="M272" t="n">
+        <v>335.67</v>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13170,7 +13218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B286"/>
+  <dimension ref="A1:B287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16033,6 +16081,16 @@
       </c>
       <c r="B286" t="n">
         <v>-0.6</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>-0.36</v>
       </c>
     </row>
   </sheetData>
@@ -16201,28 +16259,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.489140721811942</v>
+        <v>-1.480141983123221</v>
       </c>
       <c r="J2" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L2" t="n">
-        <v>0.192703433669142</v>
+        <v>0.1920451976509485</v>
       </c>
       <c r="M2" t="n">
-        <v>18.7097474438987</v>
+        <v>18.67366287648144</v>
       </c>
       <c r="N2" t="n">
-        <v>486.0181719241633</v>
+        <v>484.5824456464501</v>
       </c>
       <c r="O2" t="n">
-        <v>22.04581982880572</v>
+        <v>22.01323342097771</v>
       </c>
       <c r="P2" t="n">
-        <v>329.6023305983468</v>
+        <v>329.5042413934989</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -16283,28 +16341,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.443760998151434</v>
+        <v>-1.437373407743075</v>
       </c>
       <c r="J3" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K3" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2087135658821991</v>
+        <v>0.2085190930438445</v>
       </c>
       <c r="M3" t="n">
-        <v>17.36607087202208</v>
+        <v>17.3301200054589</v>
       </c>
       <c r="N3" t="n">
-        <v>423.0818624366019</v>
+        <v>421.6920062234919</v>
       </c>
       <c r="O3" t="n">
-        <v>20.56895384886169</v>
+        <v>20.53514076463787</v>
       </c>
       <c r="P3" t="n">
-        <v>334.7569561503738</v>
+        <v>334.6874054269666</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -16365,28 +16423,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.835257422115297</v>
+        <v>-1.81472332618512</v>
       </c>
       <c r="J4" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K4" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2155991798033966</v>
+        <v>0.2124761884645692</v>
       </c>
       <c r="M4" t="n">
-        <v>20.1071056798017</v>
+        <v>20.13517101931312</v>
       </c>
       <c r="N4" t="n">
-        <v>626.6910249788777</v>
+        <v>626.9042552187317</v>
       </c>
       <c r="O4" t="n">
-        <v>25.03379765394931</v>
+        <v>25.03805613898035</v>
       </c>
       <c r="P4" t="n">
-        <v>344.7173042916756</v>
+        <v>344.4858214884966</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -16447,28 +16505,28 @@
         <v>0.06950000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8811061925903936</v>
+        <v>-0.8798965062146707</v>
       </c>
       <c r="J5" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K5" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06761865275163204</v>
+        <v>0.06796162520791538</v>
       </c>
       <c r="M5" t="n">
-        <v>18.72815341285279</v>
+        <v>18.65651191307645</v>
       </c>
       <c r="N5" t="n">
-        <v>524.6316604630622</v>
+        <v>522.499061467394</v>
       </c>
       <c r="O5" t="n">
-        <v>22.90483923678711</v>
+        <v>22.85823837191733</v>
       </c>
       <c r="P5" t="n">
-        <v>348.8325484901729</v>
+        <v>348.8183702175458</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -16529,28 +16587,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5360146753142938</v>
+        <v>0.5443517904567816</v>
       </c>
       <c r="J6" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K6" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007643908071998551</v>
+        <v>0.007944755749735743</v>
       </c>
       <c r="M6" t="n">
-        <v>27.46217585468912</v>
+        <v>27.39235372377209</v>
       </c>
       <c r="N6" t="n">
-        <v>1866.596993129776</v>
+        <v>1859.783115593436</v>
       </c>
       <c r="O6" t="n">
-        <v>43.20413166735071</v>
+        <v>43.12520278901232</v>
       </c>
       <c r="P6" t="n">
-        <v>321.1852767047667</v>
+        <v>321.0901972221819</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -16611,28 +16669,28 @@
         <v>0.0355</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.018585743756067</v>
+        <v>-0.9858245995647263</v>
       </c>
       <c r="J7" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K7" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05060280856744193</v>
+        <v>0.04761622023618328</v>
       </c>
       <c r="M7" t="n">
-        <v>23.49033497623889</v>
+        <v>23.55582647415268</v>
       </c>
       <c r="N7" t="n">
-        <v>1026.491272900454</v>
+        <v>1029.444824616679</v>
       </c>
       <c r="O7" t="n">
-        <v>32.03890249213375</v>
+        <v>32.08496259335016</v>
       </c>
       <c r="P7" t="n">
-        <v>348.4778867230775</v>
+        <v>348.1163610253496</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -16693,28 +16751,28 @@
         <v>0.0548</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4572278065454558</v>
+        <v>0.5134498828490256</v>
       </c>
       <c r="J8" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K8" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00658930211590536</v>
+        <v>0.008285480701522574</v>
       </c>
       <c r="M8" t="n">
-        <v>30.38414864681461</v>
+        <v>30.49110797660067</v>
       </c>
       <c r="N8" t="n">
-        <v>1615.379353699624</v>
+        <v>1624.379291397307</v>
       </c>
       <c r="O8" t="n">
-        <v>40.19178216625414</v>
+        <v>40.30358906347308</v>
       </c>
       <c r="P8" t="n">
-        <v>317.5949139873241</v>
+        <v>316.9675116005508</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -16775,28 +16833,28 @@
         <v>0.0543</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8462641661586137</v>
+        <v>-0.7869532026589922</v>
       </c>
       <c r="J9" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K9" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02411619107666763</v>
+        <v>0.02079127378679735</v>
       </c>
       <c r="M9" t="n">
-        <v>30.39547025348606</v>
+        <v>30.53121904135935</v>
       </c>
       <c r="N9" t="n">
-        <v>1496.976002369906</v>
+        <v>1513.2593180881</v>
       </c>
       <c r="O9" t="n">
-        <v>38.69077412471746</v>
+        <v>38.90063390342245</v>
       </c>
       <c r="P9" t="n">
-        <v>332.6951433356546</v>
+        <v>332.0340572103536</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -16857,28 +16915,28 @@
         <v>0.0586</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.307646200157752</v>
+        <v>-1.253337841295572</v>
       </c>
       <c r="J10" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K10" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05080486936508077</v>
+        <v>0.04675489113527642</v>
       </c>
       <c r="M10" t="n">
-        <v>32.62443372719003</v>
+        <v>32.79184901353835</v>
       </c>
       <c r="N10" t="n">
-        <v>1669.839455744653</v>
+        <v>1681.67289000527</v>
       </c>
       <c r="O10" t="n">
-        <v>40.8636691419732</v>
+        <v>41.00820515464277</v>
       </c>
       <c r="P10" t="n">
-        <v>333.2565385055475</v>
+        <v>332.6591430854155</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -16939,28 +16997,28 @@
         <v>0.0709</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.040466330639022</v>
+        <v>-0.9879317271620183</v>
       </c>
       <c r="J11" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K11" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05433758763216634</v>
+        <v>0.04882422865935454</v>
       </c>
       <c r="M11" t="n">
-        <v>22.89343436541202</v>
+        <v>23.0777740983295</v>
       </c>
       <c r="N11" t="n">
-        <v>976.4151909690582</v>
+        <v>989.8693904162755</v>
       </c>
       <c r="O11" t="n">
-        <v>31.24764296661523</v>
+        <v>31.46218985411339</v>
       </c>
       <c r="P11" t="n">
-        <v>342.5945250117866</v>
+        <v>342.0129391235316</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -17021,28 +17079,28 @@
         <v>0.1599</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9177829731772563</v>
+        <v>-0.8621528179657946</v>
       </c>
       <c r="J12" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K12" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04376735866648918</v>
+        <v>0.03841381880796313</v>
       </c>
       <c r="M12" t="n">
-        <v>21.38327430274332</v>
+        <v>21.62029340441057</v>
       </c>
       <c r="N12" t="n">
-        <v>959.7406434426098</v>
+        <v>974.9104649733781</v>
       </c>
       <c r="O12" t="n">
-        <v>30.97968113849156</v>
+        <v>31.22355625122446</v>
       </c>
       <c r="P12" t="n">
-        <v>344.7438094923599</v>
+        <v>344.1331704691099</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -17103,28 +17161,28 @@
         <v>0.0668</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.433683404706399</v>
+        <v>-1.403818041238871</v>
       </c>
       <c r="J13" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K13" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1791264775562105</v>
+        <v>0.1740696859023252</v>
       </c>
       <c r="M13" t="n">
-        <v>18.40082661099636</v>
+        <v>18.38379501930113</v>
       </c>
       <c r="N13" t="n">
-        <v>487.2974491794668</v>
+        <v>485.8730883711185</v>
       </c>
       <c r="O13" t="n">
-        <v>22.07481481642523</v>
+        <v>22.0425290829142</v>
       </c>
       <c r="P13" t="n">
-        <v>359.3902665110285</v>
+        <v>359.0613740317188</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -17166,7 +17224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N271"/>
+  <dimension ref="A1:N272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36039,7 +36097,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>-42.77999685134337,173.37362350029795</t>
+          <t>-42.780034723125304,173.37376610602323</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -36064,12 +36122,84 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>-42.78312102828829,173.37203808512163</t>
+          <t>-42.78316698841155,173.3723410349494</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:46+00:00</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>-42.77632758603096,173.37577927264567</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>-42.77690392485001,173.37534091348184</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>-42.77754674588846,173.37504854033347</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>-42.77813573762278,173.37461616921348</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>-42.7788081189805,173.3744187313011</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>-42.77947256821739,173.37425356481734</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>-42.78015875196164,173.37423314098268</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>-42.7807615579052,173.3739049805924</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>-42.78133360041564,173.3734062732482</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>-42.781987638978315,173.37331411525543</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>-42.78263081864661,173.37321812728004</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>-42.78317232918008,173.37237623942448</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0403/nzd0403.xlsx
+++ b/data/nzd0403/nzd0403.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N272"/>
+  <dimension ref="A1:N273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13190,18 +13190,66 @@
         <v>386.35</v>
       </c>
       <c r="J272" t="n">
-        <v>367.72</v>
+        <v>387.61</v>
       </c>
       <c r="K272" t="n">
-        <v>382.43</v>
+        <v>394.25</v>
       </c>
       <c r="L272" t="n">
-        <v>390.7</v>
+        <v>401.11</v>
       </c>
       <c r="M272" t="n">
-        <v>335.67</v>
+        <v>366.15</v>
       </c>
       <c r="N272" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:33+00:00</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>297.56</v>
+      </c>
+      <c r="C273" t="n">
+        <v>307.94</v>
+      </c>
+      <c r="D273" t="n">
+        <v>327.05</v>
+      </c>
+      <c r="E273" t="n">
+        <v>338.18</v>
+      </c>
+      <c r="F273" t="n">
+        <v>373.21</v>
+      </c>
+      <c r="G273" t="n">
+        <v>401.26</v>
+      </c>
+      <c r="H273" t="n">
+        <v>405.29</v>
+      </c>
+      <c r="I273" t="n">
+        <v>405.77</v>
+      </c>
+      <c r="J273" t="n">
+        <v>415.92</v>
+      </c>
+      <c r="K273" t="n">
+        <v>417.02</v>
+      </c>
+      <c r="L273" t="n">
+        <v>416.3</v>
+      </c>
+      <c r="M273" t="n">
+        <v>413.86</v>
+      </c>
+      <c r="N273" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13218,7 +13266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B287"/>
+  <dimension ref="A1:B288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16091,6 +16139,16 @@
       </c>
       <c r="B287" t="n">
         <v>-0.36</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>
@@ -16259,28 +16317,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.480141983123221</v>
+        <v>-1.474051556247703</v>
       </c>
       <c r="J2" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K2" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1920451976509485</v>
+        <v>0.1920706693692431</v>
       </c>
       <c r="M2" t="n">
-        <v>18.67366287648144</v>
+        <v>18.62553441389569</v>
       </c>
       <c r="N2" t="n">
-        <v>484.5824456464501</v>
+        <v>482.9021819230263</v>
       </c>
       <c r="O2" t="n">
-        <v>22.01323342097771</v>
+        <v>21.97503542484121</v>
       </c>
       <c r="P2" t="n">
-        <v>329.5042413934989</v>
+        <v>329.4376168845128</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -16341,28 +16399,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.437373407743075</v>
+        <v>-1.428429776084686</v>
       </c>
       <c r="J3" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K3" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2085190930438445</v>
+        <v>0.2076295370053342</v>
       </c>
       <c r="M3" t="n">
-        <v>17.3301200054589</v>
+        <v>17.30676308687696</v>
       </c>
       <c r="N3" t="n">
-        <v>421.6920062234919</v>
+        <v>420.5685498348621</v>
       </c>
       <c r="O3" t="n">
-        <v>20.53514076463787</v>
+        <v>20.50776803640177</v>
       </c>
       <c r="P3" t="n">
-        <v>334.6874054269666</v>
+        <v>334.5896553504458</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -16423,28 +16481,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.81472332618512</v>
+        <v>-1.790592474895095</v>
       </c>
       <c r="J4" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2124761884645692</v>
+        <v>0.2084139657303788</v>
       </c>
       <c r="M4" t="n">
-        <v>20.13517101931312</v>
+        <v>20.18049985461286</v>
       </c>
       <c r="N4" t="n">
-        <v>626.9042552187317</v>
+        <v>628.1450725306611</v>
       </c>
       <c r="O4" t="n">
-        <v>25.03805613898035</v>
+        <v>25.06282251723977</v>
       </c>
       <c r="P4" t="n">
-        <v>344.4858214884966</v>
+        <v>344.212788697531</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -16505,28 +16563,28 @@
         <v>0.06950000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8798965062146707</v>
+        <v>-0.8693935284242366</v>
       </c>
       <c r="J5" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K5" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06796162520791538</v>
+        <v>0.06688731804747106</v>
       </c>
       <c r="M5" t="n">
-        <v>18.65651191307645</v>
+        <v>18.62173100684132</v>
       </c>
       <c r="N5" t="n">
-        <v>522.499061467394</v>
+        <v>521.0369363409199</v>
       </c>
       <c r="O5" t="n">
-        <v>22.85823837191733</v>
+        <v>22.82623351192482</v>
       </c>
       <c r="P5" t="n">
-        <v>348.8183702175458</v>
+        <v>348.6948106187833</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -16587,28 +16645,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5443517904567816</v>
+        <v>0.5741326065594455</v>
       </c>
       <c r="J6" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K6" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007944755749735743</v>
+        <v>0.008877033966198322</v>
       </c>
       <c r="M6" t="n">
-        <v>27.39235372377209</v>
+        <v>27.41627352325109</v>
       </c>
       <c r="N6" t="n">
-        <v>1859.783115593436</v>
+        <v>1857.99308437553</v>
       </c>
       <c r="O6" t="n">
-        <v>43.12520278901232</v>
+        <v>43.10444390518836</v>
       </c>
       <c r="P6" t="n">
-        <v>321.0901972221819</v>
+        <v>320.7493428657207</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -16669,28 +16727,28 @@
         <v>0.0355</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9858245995647263</v>
+        <v>-0.9248813289799411</v>
       </c>
       <c r="J7" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K7" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04761622023618328</v>
+        <v>0.04154857612358875</v>
       </c>
       <c r="M7" t="n">
-        <v>23.55582647415268</v>
+        <v>23.75465211628025</v>
       </c>
       <c r="N7" t="n">
-        <v>1029.444824616679</v>
+        <v>1049.546091196234</v>
       </c>
       <c r="O7" t="n">
-        <v>32.08496259335016</v>
+        <v>32.39669877003264</v>
       </c>
       <c r="P7" t="n">
-        <v>348.1163610253496</v>
+        <v>347.4413065960807</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -16751,28 +16809,28 @@
         <v>0.0548</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5134498828490256</v>
+        <v>0.5707358128346487</v>
       </c>
       <c r="J8" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K8" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008285480701522574</v>
+        <v>0.01017175771119372</v>
       </c>
       <c r="M8" t="n">
-        <v>30.49110797660067</v>
+        <v>30.60072896567223</v>
       </c>
       <c r="N8" t="n">
-        <v>1624.379291397307</v>
+        <v>1638.959822515883</v>
       </c>
       <c r="O8" t="n">
-        <v>40.30358906347308</v>
+        <v>40.48406874952026</v>
       </c>
       <c r="P8" t="n">
-        <v>316.9675116005508</v>
+        <v>316.3246269452468</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -16833,28 +16891,28 @@
         <v>0.0543</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7869532026589922</v>
+        <v>-0.7134570358929091</v>
       </c>
       <c r="J9" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K9" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02079127378679735</v>
+        <v>0.01691760867455661</v>
       </c>
       <c r="M9" t="n">
-        <v>30.53121904135935</v>
+        <v>30.72375306035427</v>
       </c>
       <c r="N9" t="n">
-        <v>1513.2593180881</v>
+        <v>1541.432831417813</v>
       </c>
       <c r="O9" t="n">
-        <v>38.90063390342245</v>
+        <v>39.26108545898614</v>
       </c>
       <c r="P9" t="n">
-        <v>332.0340572103536</v>
+        <v>331.2118591592013</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -16915,28 +16973,28 @@
         <v>0.0586</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.253337841295572</v>
+        <v>-1.146768253518832</v>
       </c>
       <c r="J10" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K10" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04675489113527642</v>
+        <v>0.03836699591501924</v>
       </c>
       <c r="M10" t="n">
-        <v>32.79184901353835</v>
+        <v>33.2467953727126</v>
       </c>
       <c r="N10" t="n">
-        <v>1681.67289000527</v>
+        <v>1738.687032180252</v>
       </c>
       <c r="O10" t="n">
-        <v>41.00820515464277</v>
+        <v>41.69756626207641</v>
       </c>
       <c r="P10" t="n">
-        <v>332.6591430854155</v>
+        <v>331.4832234189597</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -16997,28 +17055,28 @@
         <v>0.0709</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9879317271620183</v>
+        <v>-0.9002646935798144</v>
       </c>
       <c r="J11" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K11" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04882422865935454</v>
+        <v>0.03948236430950491</v>
       </c>
       <c r="M11" t="n">
-        <v>23.0777740983295</v>
+        <v>23.45601724959687</v>
       </c>
       <c r="N11" t="n">
-        <v>989.8693904162755</v>
+        <v>1031.110631488372</v>
       </c>
       <c r="O11" t="n">
-        <v>31.46218985411339</v>
+        <v>32.11091140855974</v>
       </c>
       <c r="P11" t="n">
-        <v>342.0129391235316</v>
+        <v>341.0392684785073</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -17079,28 +17137,28 @@
         <v>0.1599</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8621528179657946</v>
+        <v>-0.7790887143686425</v>
       </c>
       <c r="J12" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K12" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L12" t="n">
-        <v>0.03841381880796313</v>
+        <v>0.03062367498035157</v>
       </c>
       <c r="M12" t="n">
-        <v>21.62029340441057</v>
+        <v>22.01944391423149</v>
       </c>
       <c r="N12" t="n">
-        <v>974.9104649733781</v>
+        <v>1011.45295024764</v>
       </c>
       <c r="O12" t="n">
-        <v>31.22355625122446</v>
+        <v>31.80334809807987</v>
       </c>
       <c r="P12" t="n">
-        <v>344.1331704691099</v>
+        <v>343.2184363117599</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -17161,28 +17219,28 @@
         <v>0.0668</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.403818041238871</v>
+        <v>-1.310406201307693</v>
       </c>
       <c r="J13" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K13" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1740696859023252</v>
+        <v>0.1465507222320922</v>
       </c>
       <c r="M13" t="n">
-        <v>18.38379501930113</v>
+        <v>18.80063160525841</v>
       </c>
       <c r="N13" t="n">
-        <v>485.8730883711185</v>
+        <v>521.916898574392</v>
       </c>
       <c r="O13" t="n">
-        <v>22.0425290829142</v>
+        <v>22.84550061991184</v>
       </c>
       <c r="P13" t="n">
-        <v>359.0613740317188</v>
+        <v>358.0218465457168</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -17224,7 +17282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N272"/>
+  <dimension ref="A1:N273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36179,25 +36237,97 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>-42.78133360041564,173.3734062732482</t>
+          <t>-42.78138809147183,173.37363790858575</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>-42.781987638978315,173.37331411525543</t>
+          <t>-42.782015108094754,173.37345372491654</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>-42.78263081864661,173.37321812728004</t>
+          <t>-42.782650543904744,173.3733425459086</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>-42.78317232918008,173.37237623942448</t>
+          <t>-42.78322769814106,173.37274121678402</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:33+00:00</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>-42.776310869695344,173.37574256889465</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>-42.77691964680173,173.37537543399185</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>-42.77756976060583,173.3750990738493</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>-42.77818510943386,173.37473695975186</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>-42.77891255768257,173.3747207216972</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>-42.779602453751046,173.37467434988972</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>-42.7802034030957,173.37440127862186</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>-42.78081608084626,173.37413056040418</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>-42.78146564932292,173.37396760241379</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>-42.78206802400768,173.37372266874561</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>-42.78267932624279,173.3735240944607</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>-42.78331436420931,173.37331251301595</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0403/nzd0403.xlsx
+++ b/data/nzd0403/nzd0403.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N273"/>
+  <dimension ref="A1:N276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13255,6 +13255,150 @@
         </is>
       </c>
     </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>301.15</v>
+      </c>
+      <c r="C274" t="n">
+        <v>314.35</v>
+      </c>
+      <c r="D274" t="n">
+        <v>331.53</v>
+      </c>
+      <c r="E274" t="n">
+        <v>347.31</v>
+      </c>
+      <c r="F274" t="n">
+        <v>379.24</v>
+      </c>
+      <c r="G274" t="n">
+        <v>403.71</v>
+      </c>
+      <c r="H274" t="n">
+        <v>403.32</v>
+      </c>
+      <c r="I274" t="n">
+        <v>407.66</v>
+      </c>
+      <c r="J274" t="n">
+        <v>414.28</v>
+      </c>
+      <c r="K274" t="n">
+        <v>419.38</v>
+      </c>
+      <c r="L274" t="n">
+        <v>422.03</v>
+      </c>
+      <c r="M274" t="n">
+        <v>417.96</v>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>303.49</v>
+      </c>
+      <c r="C275" t="n">
+        <v>315.52</v>
+      </c>
+      <c r="D275" t="n">
+        <v>333.31</v>
+      </c>
+      <c r="E275" t="n">
+        <v>347.5</v>
+      </c>
+      <c r="F275" t="n">
+        <v>378.33</v>
+      </c>
+      <c r="G275" t="n">
+        <v>397.2</v>
+      </c>
+      <c r="H275" t="n">
+        <v>402.06</v>
+      </c>
+      <c r="I275" t="n">
+        <v>406.39</v>
+      </c>
+      <c r="J275" t="n">
+        <v>414.1</v>
+      </c>
+      <c r="K275" t="n">
+        <v>418.91</v>
+      </c>
+      <c r="L275" t="n">
+        <v>426.09</v>
+      </c>
+      <c r="M275" t="n">
+        <v>424.05</v>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>304.56</v>
+      </c>
+      <c r="C276" t="n">
+        <v>320.12</v>
+      </c>
+      <c r="D276" t="n">
+        <v>337.17</v>
+      </c>
+      <c r="E276" t="n">
+        <v>353.23</v>
+      </c>
+      <c r="F276" t="n">
+        <v>381.21</v>
+      </c>
+      <c r="G276" t="n">
+        <v>397.2</v>
+      </c>
+      <c r="H276" t="n">
+        <v>406.29</v>
+      </c>
+      <c r="I276" t="n">
+        <v>409.7</v>
+      </c>
+      <c r="J276" t="n">
+        <v>414.1</v>
+      </c>
+      <c r="K276" t="n">
+        <v>418.91</v>
+      </c>
+      <c r="L276" t="n">
+        <v>426.09</v>
+      </c>
+      <c r="M276" t="n">
+        <v>429.37</v>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13266,7 +13410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B288"/>
+  <dimension ref="A1:B291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16149,6 +16293,36 @@
       </c>
       <c r="B288" t="n">
         <v>0.35</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>0.63</v>
       </c>
     </row>
   </sheetData>
@@ -16317,28 +16491,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.474051556247703</v>
+        <v>-1.443402524248251</v>
       </c>
       <c r="J2" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K2" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1920706693692431</v>
+        <v>0.1889835007290166</v>
       </c>
       <c r="M2" t="n">
-        <v>18.62553441389569</v>
+        <v>18.53312837380336</v>
       </c>
       <c r="N2" t="n">
-        <v>482.9021819230263</v>
+        <v>479.2187974971143</v>
       </c>
       <c r="O2" t="n">
-        <v>21.97503542484121</v>
+        <v>21.8910666139664</v>
       </c>
       <c r="P2" t="n">
-        <v>329.4376168845128</v>
+        <v>329.1014203942826</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -16399,28 +16573,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.428429776084686</v>
+        <v>-1.382922712291518</v>
       </c>
       <c r="J3" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K3" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2076295370053342</v>
+        <v>0.1992991728517253</v>
       </c>
       <c r="M3" t="n">
-        <v>17.30676308687696</v>
+        <v>17.32915376688222</v>
       </c>
       <c r="N3" t="n">
-        <v>420.5685498348621</v>
+        <v>420.3622010602664</v>
       </c>
       <c r="O3" t="n">
-        <v>20.50776803640177</v>
+        <v>20.50273642859085</v>
       </c>
       <c r="P3" t="n">
-        <v>334.5896553504458</v>
+        <v>334.090834552045</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -16481,28 +16655,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.790592474895095</v>
+        <v>-1.705085733354869</v>
       </c>
       <c r="J4" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K4" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2084139657303788</v>
+        <v>0.1925739252711287</v>
       </c>
       <c r="M4" t="n">
-        <v>20.18049985461286</v>
+        <v>20.37782292588776</v>
       </c>
       <c r="N4" t="n">
-        <v>628.1450725306611</v>
+        <v>636.7024838158754</v>
       </c>
       <c r="O4" t="n">
-        <v>25.06282251723977</v>
+        <v>25.23296422967138</v>
       </c>
       <c r="P4" t="n">
-        <v>344.212788697531</v>
+        <v>343.2426018296158</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -16563,28 +16737,28 @@
         <v>0.06950000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8693935284242366</v>
+        <v>-0.8124403514495299</v>
       </c>
       <c r="J5" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K5" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06688731804747106</v>
+        <v>0.05953149537351565</v>
       </c>
       <c r="M5" t="n">
-        <v>18.62173100684132</v>
+        <v>18.61582504208648</v>
       </c>
       <c r="N5" t="n">
-        <v>521.0369363409199</v>
+        <v>521.4883810341137</v>
       </c>
       <c r="O5" t="n">
-        <v>22.82623351192482</v>
+        <v>22.83612009589444</v>
       </c>
       <c r="P5" t="n">
-        <v>348.6948106187833</v>
+        <v>348.0228888974117</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -16645,28 +16819,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5741326065594455</v>
+        <v>0.6744904505984421</v>
       </c>
       <c r="J6" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K6" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008877033966198322</v>
+        <v>0.01236856069708303</v>
       </c>
       <c r="M6" t="n">
-        <v>27.41627352325109</v>
+        <v>27.54138310344252</v>
       </c>
       <c r="N6" t="n">
-        <v>1857.99308437553</v>
+        <v>1857.631061227845</v>
       </c>
       <c r="O6" t="n">
-        <v>43.10444390518836</v>
+        <v>43.10024432909685</v>
       </c>
       <c r="P6" t="n">
-        <v>320.7493428657207</v>
+        <v>319.5976048772001</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -16727,28 +16901,28 @@
         <v>0.0355</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9248813289799411</v>
+        <v>-0.7535680978070911</v>
       </c>
       <c r="J7" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K7" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04154857612358875</v>
+        <v>0.0269905428386884</v>
       </c>
       <c r="M7" t="n">
-        <v>23.75465211628025</v>
+        <v>24.3053384962539</v>
       </c>
       <c r="N7" t="n">
-        <v>1049.546091196234</v>
+        <v>1102.57847505287</v>
       </c>
       <c r="O7" t="n">
-        <v>32.39669877003264</v>
+        <v>33.20509712458119</v>
       </c>
       <c r="P7" t="n">
-        <v>347.4413065960807</v>
+        <v>345.5384332586694</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -16809,28 +16983,28 @@
         <v>0.0548</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5707358128346487</v>
+        <v>0.7324761677103587</v>
       </c>
       <c r="J8" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K8" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01017175771119372</v>
+        <v>0.01647965479930369</v>
       </c>
       <c r="M8" t="n">
-        <v>30.60072896567223</v>
+        <v>30.919835104765</v>
       </c>
       <c r="N8" t="n">
-        <v>1638.959822515883</v>
+        <v>1676.993928226598</v>
       </c>
       <c r="O8" t="n">
-        <v>40.48406874952026</v>
+        <v>40.95111632454722</v>
       </c>
       <c r="P8" t="n">
-        <v>316.3246269452468</v>
+        <v>314.5045928459262</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -16891,28 +17065,28 @@
         <v>0.0543</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7134570358929091</v>
+        <v>-0.4969968069234291</v>
       </c>
       <c r="J9" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K9" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01691760867455661</v>
+        <v>0.007962085997845647</v>
       </c>
       <c r="M9" t="n">
-        <v>30.72375306035427</v>
+        <v>31.30932427446606</v>
       </c>
       <c r="N9" t="n">
-        <v>1541.432831417813</v>
+        <v>1624.541417723915</v>
       </c>
       <c r="O9" t="n">
-        <v>39.26108545898614</v>
+        <v>40.30560032705027</v>
       </c>
       <c r="P9" t="n">
-        <v>331.2118591592013</v>
+        <v>328.7836973173638</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -16973,28 +17147,28 @@
         <v>0.0586</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.146768253518832</v>
+        <v>-0.8890297049368847</v>
       </c>
       <c r="J10" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K10" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03836699591501924</v>
+        <v>0.02220950918090714</v>
       </c>
       <c r="M10" t="n">
-        <v>33.2467953727126</v>
+        <v>34.29945821493803</v>
       </c>
       <c r="N10" t="n">
-        <v>1738.687032180252</v>
+        <v>1860.175267997765</v>
       </c>
       <c r="O10" t="n">
-        <v>41.69756626207641</v>
+        <v>43.12974922252348</v>
       </c>
       <c r="P10" t="n">
-        <v>331.4832234189597</v>
+        <v>328.6300152890522</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -17055,28 +17229,28 @@
         <v>0.0709</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9002646935798144</v>
+        <v>-0.6697498722943144</v>
       </c>
       <c r="J11" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K11" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03948236430950491</v>
+        <v>0.02054903382076834</v>
       </c>
       <c r="M11" t="n">
-        <v>23.45601724959687</v>
+        <v>24.42713862781079</v>
       </c>
       <c r="N11" t="n">
-        <v>1031.110631488372</v>
+        <v>1132.924820952076</v>
       </c>
       <c r="O11" t="n">
-        <v>32.11091140855974</v>
+        <v>33.65894860140578</v>
       </c>
       <c r="P11" t="n">
-        <v>341.0392684785073</v>
+        <v>338.4711718417519</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -17137,28 +17311,28 @@
         <v>0.1599</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7790887143686425</v>
+        <v>-0.5446012231937554</v>
       </c>
       <c r="J12" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K12" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="L12" t="n">
-        <v>0.03062367498035157</v>
+        <v>0.01399517132792072</v>
       </c>
       <c r="M12" t="n">
-        <v>22.01944391423149</v>
+        <v>23.13013147577277</v>
       </c>
       <c r="N12" t="n">
-        <v>1011.45295024764</v>
+        <v>1115.156453745611</v>
       </c>
       <c r="O12" t="n">
-        <v>31.80334809807987</v>
+        <v>33.39395834197574</v>
       </c>
       <c r="P12" t="n">
-        <v>343.2184363117599</v>
+        <v>340.6282756713049</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -17219,28 +17393,28 @@
         <v>0.0668</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.310406201307693</v>
+        <v>-1.086316189986831</v>
       </c>
       <c r="J13" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K13" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1465507222320922</v>
+        <v>0.09071198327437557</v>
       </c>
       <c r="M13" t="n">
-        <v>18.80063160525841</v>
+        <v>19.75478122269701</v>
       </c>
       <c r="N13" t="n">
-        <v>521.916898574392</v>
+        <v>625.3803187700018</v>
       </c>
       <c r="O13" t="n">
-        <v>22.84550061991184</v>
+        <v>25.00760521861303</v>
       </c>
       <c r="P13" t="n">
-        <v>358.0218465457168</v>
+        <v>355.5189697155941</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -17282,7 +17456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N273"/>
+  <dimension ref="A1:N276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36333,6 +36507,222 @@
         </is>
       </c>
     </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>-42.7763278701612,173.37577989650563</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>-42.776950001504076,173.37544208358</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>-42.777590975798596,173.37514565621794</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>-42.77822500001562,173.37483455437084</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>-42.77893563435611,173.37478744964918</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>-42.77961098048006,173.37470197383695</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>-42.78019738650728,173.3743786225785</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>-42.78082138712306,173.37415251438216</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>-42.781461156417954,173.37394850320825</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>-42.78207350844899,173.3737505434943</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>-42.78269018349483,173.37359257858571</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>-42.78332181179931,173.37336160792384</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>-42.77633895123817,173.37580422704852</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>-42.776955542061735,173.37545424895643</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>-42.77759940504397,173.37516416440002</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>-42.77822583015827,173.37483658536644</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>-42.77893215180921,173.37477737959023</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>-42.77958832372822,173.37462857307943</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>-42.78019353833162,173.37436413191347</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>-42.78081782153012,173.37413776223784</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>-42.781460663294055,173.37394640695413</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>-42.782072416209104,173.37374499216682</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>-42.782697876392014,173.37364110312842</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>-42.78333287415624,173.37343453184508</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>-42.77634401822463,173.3758153525561</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>-42.77697732543816,173.3755020786626</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>-42.77761768418368,173.37520430013788</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>-42.778250865495856,173.37489783594302</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>-42.778943173493026,173.3748092496707</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>-42.77958832372822,173.37462857307943</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>-42.78020645719977,173.37441277915315</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>-42.78082711452821,173.3741762107435</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>-42.781460663294055,173.37394640695413</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>-42.782072416209104,173.37374499216682</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>-42.782697876392014,173.37364110312842</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>-42.78334253778625,173.37349823552142</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0403/nzd0403.xlsx
+++ b/data/nzd0403/nzd0403.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N276"/>
+  <dimension ref="A1:N277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13373,7 +13373,7 @@
         <v>381.21</v>
       </c>
       <c r="G276" t="n">
-        <v>397.2</v>
+        <v>402.52</v>
       </c>
       <c r="H276" t="n">
         <v>406.29</v>
@@ -13382,18 +13382,66 @@
         <v>409.7</v>
       </c>
       <c r="J276" t="n">
-        <v>414.1</v>
+        <v>386.31</v>
       </c>
       <c r="K276" t="n">
-        <v>418.91</v>
+        <v>389.24</v>
       </c>
       <c r="L276" t="n">
-        <v>426.09</v>
+        <v>394.74</v>
       </c>
       <c r="M276" t="n">
         <v>429.37</v>
       </c>
       <c r="N276" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>306.16</v>
+      </c>
+      <c r="C277" t="n">
+        <v>327.32</v>
+      </c>
+      <c r="D277" t="n">
+        <v>341.58</v>
+      </c>
+      <c r="E277" t="n">
+        <v>362.97</v>
+      </c>
+      <c r="F277" t="n">
+        <v>382.47</v>
+      </c>
+      <c r="G277" t="n">
+        <v>404.1</v>
+      </c>
+      <c r="H277" t="n">
+        <v>407.49</v>
+      </c>
+      <c r="I277" t="n">
+        <v>414.4</v>
+      </c>
+      <c r="J277" t="n">
+        <v>362.58</v>
+      </c>
+      <c r="K277" t="n">
+        <v>365.87</v>
+      </c>
+      <c r="L277" t="n">
+        <v>371.24</v>
+      </c>
+      <c r="M277" t="n">
+        <v>436.47</v>
+      </c>
+      <c r="N277" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13410,7 +13458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B291"/>
+  <dimension ref="A1:B292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16323,6 +16371,16 @@
       </c>
       <c r="B291" t="n">
         <v>0.63</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
@@ -16491,28 +16549,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.443402524248251</v>
+        <v>-1.431152719312647</v>
       </c>
       <c r="J2" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K2" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1889835007290166</v>
+        <v>0.1873760279686338</v>
       </c>
       <c r="M2" t="n">
-        <v>18.53312837380336</v>
+        <v>18.51165870823181</v>
       </c>
       <c r="N2" t="n">
-        <v>479.2187974971143</v>
+        <v>478.3147026397535</v>
       </c>
       <c r="O2" t="n">
-        <v>21.8910666139664</v>
+        <v>21.8704070067238</v>
       </c>
       <c r="P2" t="n">
-        <v>329.1014203942826</v>
+        <v>328.9666941453552</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -16573,28 +16631,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.382922712291518</v>
+        <v>-1.360377904285458</v>
       </c>
       <c r="J3" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K3" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1992991728517253</v>
+        <v>0.1940624662153037</v>
       </c>
       <c r="M3" t="n">
-        <v>17.32915376688222</v>
+        <v>17.37179931842651</v>
       </c>
       <c r="N3" t="n">
-        <v>420.3622010602664</v>
+        <v>422.2291119463432</v>
       </c>
       <c r="O3" t="n">
-        <v>20.50273642859085</v>
+        <v>20.54821432500506</v>
       </c>
       <c r="P3" t="n">
-        <v>334.090834552045</v>
+        <v>333.8430237098719</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -16655,28 +16713,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.705085733354869</v>
+        <v>-1.671944039285909</v>
       </c>
       <c r="J4" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K4" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1925739252711287</v>
+        <v>0.1860037443457966</v>
       </c>
       <c r="M4" t="n">
-        <v>20.37782292588776</v>
+        <v>20.47623546732988</v>
       </c>
       <c r="N4" t="n">
-        <v>636.7024838158754</v>
+        <v>641.5730050929119</v>
       </c>
       <c r="O4" t="n">
-        <v>25.23296422967138</v>
+        <v>25.32929144474657</v>
       </c>
       <c r="P4" t="n">
-        <v>343.2426018296158</v>
+        <v>342.8655286968826</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -16737,28 +16795,28 @@
         <v>0.06950000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8124403514495299</v>
+        <v>-0.7834286387750213</v>
       </c>
       <c r="J5" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K5" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05953149537351565</v>
+        <v>0.0554664208918243</v>
       </c>
       <c r="M5" t="n">
-        <v>18.61582504208648</v>
+        <v>18.65246908391653</v>
       </c>
       <c r="N5" t="n">
-        <v>521.4883810341137</v>
+        <v>524.7333527399766</v>
       </c>
       <c r="O5" t="n">
-        <v>22.83612009589444</v>
+        <v>22.90705901550822</v>
       </c>
       <c r="P5" t="n">
-        <v>348.0228888974117</v>
+        <v>347.6796733876863</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -16819,28 +16877,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6744904505984421</v>
+        <v>0.7087551450264655</v>
       </c>
       <c r="J6" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K6" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01236856069708303</v>
+        <v>0.01369212813321841</v>
       </c>
       <c r="M6" t="n">
-        <v>27.54138310344252</v>
+        <v>27.58718153151973</v>
       </c>
       <c r="N6" t="n">
-        <v>1857.631061227845</v>
+        <v>1858.107009103747</v>
       </c>
       <c r="O6" t="n">
-        <v>43.10024432909685</v>
+        <v>43.10576538125436</v>
       </c>
       <c r="P6" t="n">
-        <v>319.5976048772001</v>
+        <v>319.2033005425346</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -16901,28 +16959,28 @@
         <v>0.0355</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7535680978070911</v>
+        <v>-0.6912946732518245</v>
       </c>
       <c r="J7" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K7" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0269905428386884</v>
+        <v>0.02246238308563908</v>
       </c>
       <c r="M7" t="n">
-        <v>24.3053384962539</v>
+        <v>24.52655646023107</v>
       </c>
       <c r="N7" t="n">
-        <v>1102.57847505287</v>
+        <v>1124.67101127237</v>
       </c>
       <c r="O7" t="n">
-        <v>33.20509712458119</v>
+        <v>33.53611502950766</v>
       </c>
       <c r="P7" t="n">
-        <v>345.5384332586694</v>
+        <v>344.8448102061963</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -16983,28 +17041,28 @@
         <v>0.0548</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7324761677103587</v>
+        <v>0.7868789771736295</v>
       </c>
       <c r="J8" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K8" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01647965479930369</v>
+        <v>0.0188988668908121</v>
       </c>
       <c r="M8" t="n">
-        <v>30.919835104765</v>
+        <v>31.03740823107842</v>
       </c>
       <c r="N8" t="n">
-        <v>1676.993928226598</v>
+        <v>1690.480184590092</v>
       </c>
       <c r="O8" t="n">
-        <v>40.95111632454722</v>
+        <v>41.11544946355435</v>
       </c>
       <c r="P8" t="n">
-        <v>314.5045928459262</v>
+        <v>313.8907299134661</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -17065,28 +17123,28 @@
         <v>0.0543</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4969968069234291</v>
+        <v>-0.4228793637003715</v>
       </c>
       <c r="J9" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K9" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L9" t="n">
-        <v>0.007962085997845647</v>
+        <v>0.005695169189623872</v>
       </c>
       <c r="M9" t="n">
-        <v>31.30932427446606</v>
+        <v>31.54753672513792</v>
       </c>
       <c r="N9" t="n">
-        <v>1624.541417723915</v>
+        <v>1654.917831792327</v>
       </c>
       <c r="O9" t="n">
-        <v>40.30560032705027</v>
+        <v>40.68068130934298</v>
       </c>
       <c r="P9" t="n">
-        <v>328.7836973173638</v>
+        <v>327.9499654211758</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -17147,28 +17205,28 @@
         <v>0.0586</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8890297049368847</v>
+        <v>-0.8663343282460563</v>
       </c>
       <c r="J10" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K10" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02220950918090714</v>
+        <v>0.02136628414878883</v>
       </c>
       <c r="M10" t="n">
-        <v>34.29945821493803</v>
+        <v>34.29716807949939</v>
       </c>
       <c r="N10" t="n">
-        <v>1860.175267997765</v>
+        <v>1845.662132686027</v>
       </c>
       <c r="O10" t="n">
-        <v>43.12974922252348</v>
+        <v>42.96117005722758</v>
       </c>
       <c r="P10" t="n">
-        <v>328.6300152890522</v>
+        <v>328.377644349931</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -17229,28 +17287,28 @@
         <v>0.0709</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6697498722943144</v>
+        <v>-0.657928173593657</v>
       </c>
       <c r="J11" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K11" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02054903382076834</v>
+        <v>0.02019152469467012</v>
       </c>
       <c r="M11" t="n">
-        <v>24.42713862781079</v>
+        <v>24.39963701091695</v>
       </c>
       <c r="N11" t="n">
-        <v>1132.924820952076</v>
+        <v>1117.805980211043</v>
       </c>
       <c r="O11" t="n">
-        <v>33.65894860140578</v>
+        <v>33.43360555206457</v>
       </c>
       <c r="P11" t="n">
-        <v>338.4711718417519</v>
+        <v>338.3386481825936</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -17311,28 +17369,28 @@
         <v>0.1599</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5446012231937554</v>
+        <v>-0.5339831320276144</v>
       </c>
       <c r="J12" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K12" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01399517132792072</v>
+        <v>0.01372154215955346</v>
       </c>
       <c r="M12" t="n">
-        <v>23.13013147577277</v>
+        <v>23.10384673564395</v>
       </c>
       <c r="N12" t="n">
-        <v>1115.156453745611</v>
+        <v>1098.62973014966</v>
       </c>
       <c r="O12" t="n">
-        <v>33.39395834197574</v>
+        <v>33.14558387100249</v>
       </c>
       <c r="P12" t="n">
-        <v>340.6282756713049</v>
+        <v>340.5101828040586</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -17393,28 +17451,28 @@
         <v>0.0668</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.086316189986831</v>
+        <v>-1.005202357304422</v>
       </c>
       <c r="J13" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K13" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09071198327437557</v>
+        <v>0.07441037920538551</v>
       </c>
       <c r="M13" t="n">
-        <v>19.75478122269701</v>
+        <v>20.11019904935186</v>
       </c>
       <c r="N13" t="n">
-        <v>625.3803187700018</v>
+        <v>667.2679995513674</v>
       </c>
       <c r="O13" t="n">
-        <v>25.00760521861303</v>
+        <v>25.83153111124789</v>
       </c>
       <c r="P13" t="n">
-        <v>355.5189697155941</v>
+        <v>354.6105316443708</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -17456,7 +17514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N276"/>
+  <dimension ref="A1:N277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36684,7 +36742,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>-42.77958832372822,173.37462857307943</t>
+          <t>-42.77960683892681,173.3746885564902</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -36699,17 +36757,17 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>-42.781460663294055,173.37394640695413</t>
+          <t>-42.781384529979256,173.37362276900888</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>-42.782072416209104,173.37374499216682</t>
+          <t>-42.78200346511447,173.3733945502483</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>-42.782697876392014,173.37364110312842</t>
+          <t>-42.78263847380612,173.37326641269433</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -36718,6 +36776,78 @@
         </is>
       </c>
       <c r="N276" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>-42.77635159502475,173.37583198883243</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>-42.77701142111728,173.37557694261764</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>-42.77763856784662,173.37525015472733</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>-42.77829342112473,173.37500195134655</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>-42.77894799547689,173.3748231928344</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>-42.77961233779549,173.37470637111906</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>-42.78021012212311,173.37442657979216</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>-42.78084031000171,173.37423080531798</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>-42.7813195186886,173.37334641380474</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>-42.781949154040596,173.37311852019988</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>-42.782593944745805,173.37298554473128</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>-42.783355434680715,173.3735832536162</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
